--- a/Internal_safety_audit_CAP_tracker_15_10_2026..xlsx
+++ b/Internal_safety_audit_CAP_tracker_15_10_2026..xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Furb-X\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fdavronov\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B6C7E72-89AF-4B48-98B9-76598D72E1C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD1E8952-ACA8-4772-95F4-90047E6E57A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Audit findings" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Audit findings'!$4:$4</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -316,7 +316,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -339,28 +339,14 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="4">
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <font>
         <b/>
@@ -391,6 +377,17 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1995,9 +1992,9 @@
         <v>47</v>
       </c>
       <c r="H5" s="6"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="10"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
     </row>
     <row r="6" spans="1:11" ht="229.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
@@ -2018,9 +2015,9 @@
         <v>47</v>
       </c>
       <c r="H6" s="6"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
-      <c r="K6" s="10"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
     </row>
     <row r="7" spans="1:11" ht="229.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
@@ -2043,9 +2040,9 @@
         <v>46</v>
       </c>
       <c r="H7" s="6"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
     </row>
     <row r="8" spans="1:11" ht="229.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
@@ -2066,9 +2063,9 @@
         <v>16</v>
       </c>
       <c r="H8" s="6"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="10"/>
-      <c r="K8" s="10"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
     </row>
     <row r="9" spans="1:11" ht="229.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
@@ -2089,9 +2086,9 @@
         <v>16</v>
       </c>
       <c r="H9" s="6"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="10"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
     </row>
     <row r="10" spans="1:11" ht="229.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5">
@@ -2112,11 +2109,11 @@
         <v>47</v>
       </c>
       <c r="H10" s="6"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="11">
+      <c r="I10" s="6"/>
+      <c r="J10" s="10">
         <v>46316</v>
       </c>
-      <c r="K10" s="10"/>
+      <c r="K10" s="6"/>
     </row>
     <row r="11" spans="1:11" ht="229.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
@@ -2137,11 +2134,11 @@
         <v>47</v>
       </c>
       <c r="H11" s="6"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="11">
+      <c r="I11" s="6"/>
+      <c r="J11" s="10">
         <v>46316</v>
       </c>
-      <c r="K11" s="10"/>
+      <c r="K11" s="6"/>
     </row>
     <row r="12" spans="1:11" ht="229.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
@@ -2162,9 +2159,9 @@
         <v>16</v>
       </c>
       <c r="H12" s="6"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="10"/>
-      <c r="K12" s="10"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
+      <c r="K12" s="6"/>
     </row>
     <row r="13" spans="1:11" ht="229.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
@@ -2185,9 +2182,9 @@
         <v>47</v>
       </c>
       <c r="H13" s="6"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="10"/>
-      <c r="K13" s="10"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
     </row>
     <row r="14" spans="1:11" ht="229.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5">
@@ -2208,9 +2205,9 @@
         <v>16</v>
       </c>
       <c r="H14" s="6"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="10"/>
-      <c r="K14" s="10"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
+      <c r="K14" s="6"/>
     </row>
     <row r="15" spans="1:11" ht="229.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
@@ -2231,9 +2228,9 @@
         <v>47</v>
       </c>
       <c r="H15" s="6"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
-      <c r="K15" s="10"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
+      <c r="K15" s="6"/>
     </row>
     <row r="16" spans="1:11" ht="229.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5">
@@ -2254,9 +2251,9 @@
         <v>47</v>
       </c>
       <c r="H16" s="6"/>
-      <c r="I16" s="10"/>
-      <c r="J16" s="10"/>
-      <c r="K16" s="10"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
     </row>
     <row r="17" spans="1:11" ht="229.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
@@ -2277,9 +2274,9 @@
         <v>16</v>
       </c>
       <c r="H17" s="6"/>
-      <c r="I17" s="10"/>
-      <c r="J17" s="10"/>
-      <c r="K17" s="10"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
     </row>
     <row r="18" spans="1:11" ht="229.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5">
@@ -2300,25 +2297,25 @@
         <v>16</v>
       </c>
       <c r="H18" s="6"/>
-      <c r="I18" s="10"/>
-      <c r="J18" s="10"/>
-      <c r="K18" s="10"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6"/>
+      <c r="K18" s="6"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="F5:F18">
+    <cfRule type="expression" dxfId="3" priority="5">
+      <formula>AND(F5&lt;&gt;"",F5&lt;TODAY(),$G5&lt;&gt;"Closed")</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="G5:G18">
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
       <formula>"Closed"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
       <formula>"In progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
       <formula>"Open"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F5:F18">
-    <cfRule type="expression" dxfId="0" priority="5">
-      <formula>AND(F5&lt;&gt;"",F5&lt;TODAY(),$G5&lt;&gt;"Closed")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
@@ -2333,6 +2330,9 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;11&amp;KA80000 PUBLIC</oddFooter>
+  </headerFooter>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>